--- a/tests/fixtures/16_bundesliga/16_bundesliga_pattern-from-claude.xlsx
+++ b/tests/fixtures/16_bundesliga/16_bundesliga_pattern-from-claude.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
